--- a/ig/ch-term/ValueSet-edqm-routeofadministration.xlsx
+++ b/ig/ch-term/ValueSet-edqm-routeofadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-02-09T14:38:25+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Valueset RouteOfAdministration from EDQM, ROA, export 1.6.2021, see https://standardterms.edqm.eu/#</t>
+    <t>Valueset RouteOfAdministration from EDQM, ROA, export 1.6.2021, see https://standardterms.edqm.eu/\#</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -604,6 +604,12 @@
   </si>
   <si>
     <t>Intraputaminal use</t>
+  </si>
+  <si>
+    <t>20088000</t>
+  </si>
+  <si>
+    <t>Perilesional use</t>
   </si>
   <si>
     <t/>
@@ -894,7 +900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1570,15 +1576,23 @@
         <v>197</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>199</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
